--- a/travel-log-template.xlsx
+++ b/travel-log-template.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5880" yWindow="1344" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="지출내역" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="입력 가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="예산 설정" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="입력 가이드" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="12">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -29,13 +29,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="003730A3"/>
+      <color rgb="FF3730A3"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -47,8 +47,50 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF3730A3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF007700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF007700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF007700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -57,22 +99,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2FF"/>
+        <fgColor rgb="FFEEF2FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F7CFF"/>
+        <fgColor rgb="FF4F7CFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8F9FF"/>
+        <fgColor rgb="FFF8F9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0FFF4"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,54 +138,89 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -496,496 +583,311 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" style="17" min="1" max="1"/>
+    <col width="16" customWidth="1" style="17" min="2" max="3"/>
+    <col width="30" customWidth="1" style="17" min="4" max="4"/>
+    <col width="12" customWidth="1" style="17" min="5" max="5"/>
+    <col width="10" customWidth="1" style="17" min="6" max="6"/>
+    <col width="8" customWidth="1" style="17" min="7" max="7"/>
+    <col width="22" customWidth="1" style="17" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="17">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>📋 여행 지출 기록부 — 3행부터 데이터 입력 (헤더 행 수정 금지)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="22.05" customHeight="1" s="17">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+    <row r="3" ht="19.95" customHeight="1" s="17">
+      <c r="A3" s="19" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>바르셀로나 편도</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>504400</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>중국동방항공 경유</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="19.95" customHeight="1" s="17">
+      <c r="A4" s="18" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>shopping</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>에이블리 옷 삼</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>50550</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="19.95" customHeight="1" s="17">
+      <c r="A5" s="19" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>shopping</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>베드버그, 모기기피제</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>14810</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="19.95" customHeight="1" s="17">
+      <c r="A6" s="18" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>accommodation</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Dayin International Youth Hostel</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>21649</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="19.95" customHeight="1" s="17">
+      <c r="A7" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>accommodation</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Barcelona hostel 3 nights</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>TOC Hostel Barcelona</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>279174</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>3박 일괄결제</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>도시세 추가 36,834</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.95" customHeight="1" s="17">
+      <c r="A8" s="18" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Tapas dinner</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>attraction</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>보케리아시장/고딕지구/벙커야경</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>29900</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>맛있었음</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="19.95" customHeight="1" s="17">
+      <c r="A9" s="19" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>transport</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Metro day pass</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>11.35</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>attraction</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>사그라다파밀리아 입장 16:45</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>54931</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>attraction</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Sagrada Familia</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Lunch + coffee</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>accommodation</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Madrid hostel 2 nights</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>90000</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Churros con chocolate</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>attraction</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Prado Museum</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Lisbon</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>transport</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Bus Madrid-Lisbon</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Lisbon</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>accommodation</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Lisbon hostel 3 nights</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>135000</v>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Lisbon</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Pastel de nata + lunch</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Lisbon</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>shopping</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>기념품</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>부킹닷컴</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C3:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C194" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"accommodation,food,transport,attraction,shopping,etc"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F3:F194" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"KRW,EUR"</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="G3:G194" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole">
       <formula1>1</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -1000,258 +902,526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" style="17" min="1" max="1"/>
+    <col width="16" customWidth="1" style="17" min="2" max="2"/>
+    <col width="30" customWidth="1" style="17" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="17">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액 (KRW)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="17">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>── 총 예산 ──</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="9" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="17">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>total_budget</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>전체 여행 예산 (Google Sheet city=Budget 행으로도 입력 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="17">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="17">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>── 고정 공제 항목 ──</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="9" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="17">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>deduct_flight</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>항공권 (왕복 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="17">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>deduct_transport</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>도시 간 이동비 (버스·기차 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="17">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>deduct_emergency</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>비상금</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="17">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="17">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>── 자동 계산 ──</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="17">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>total_deductions</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>"= 항공권 + 이동 + 비상금"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="17">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>living_budget</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>"=총예산 - 공제 합계"</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="17">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="17">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>── 시나리오 ──</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="17">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>scenario1_daily</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>시나리오1: 10만원/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="17">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>scenario1_days</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>=@생활비 /@ 일예산 (자동 계산됨)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>scenario2_daily</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>125000</v>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>시나리오2: 12.5만원/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="17">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>scenario2_days</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>=@생활비 /@ 일예산'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="17">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>scenario3_daily</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>시나리오3: 15만원/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="17">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>scenario3_days</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>=@생활비 /@ 일예산'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <cols>
+    <col width="18" customWidth="1" style="17" min="1" max="1"/>
+    <col width="32" customWidth="1" style="17" min="2" max="2"/>
+    <col width="26" customWidth="1" style="17" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1" s="17">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>컬럼</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="2" ht="18" customHeight="1" s="17">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>결제일 / 지출 시작일 (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="17">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>도시명</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Barcelona</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="17">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>지출 분야 (드롭다운 선택)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>accommodation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="17">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>세부 항목명</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Barcelona hostel 3 nights</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="18" customHeight="1" s="17">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>결제 금액 (숫자만)</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>180000</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="17">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>통화 — KRW 또는 EUR</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="18" customHeight="1" s="17">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>몇 일에 나눠 반영할지 (숙소 3박 → 3)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="18" customHeight="1" s="17">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>메모 (선택)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>3박치 일괄결제</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="10" ht="18" customHeight="1" s="17">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="17">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>카테고리 목록</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="17">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>accommodation</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>숙소</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="C12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="17">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>food</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>식비</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="C13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="17">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>transport</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>교통</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="C14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="17">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>attraction</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>관광 / 입장료</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="C15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="17">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>shopping</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>쇼핑</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="C16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>etc</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr"/>
+      <c r="C17" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
